--- a/laboratorio_v3/public/templates/NEXUS_RETAIL_LAB01_EJ04_INVENTARIO.xlsx
+++ b/laboratorio_v3/public/templates/NEXUS_RETAIL_LAB01_EJ04_INVENTARIO.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="192">
   <si>
     <t xml:space="preserve">NEXUS RETAIL -- LABORATORIO 1: AI REVENUE &amp; INVENTORY COPILOT</t>
   </si>
@@ -107,6 +107,12 @@
     <t xml:space="preserve">Ejercicio 1: clasificacion de portfolio (CORE / REVIEW) por subgrupo. Ejercicio 3: un forecast de demanda a 90 dias para varios productos -- ese forecast les dio el promedio esperado; a este ejercicio le falta la dispersion alrededor de ese promedio, que es lo que van a calcular aca.</t>
   </si>
   <si>
+    <t xml:space="preserve">Convencion de calculo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venta promedio diaria = suma de los 12 meses / 365. Cobertura operativa base = 1.5 x lead time (es tambien el DDI minimo de seguridad). Inventario objetivo = venta diaria x cobertura base x (1 + % stock de seguridad). Usen esta convencion para que todos los equipos lleguen a numeros comparables.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dinamica</t>
   </si>
   <si>
@@ -233,7 +239,7 @@
     <t xml:space="preserve">Rango de stock de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">Piso y techo de % de stock de seguridad, segun la banda de variabilidad del Modulo 5.</t>
+    <t xml:space="preserve">Piso y techo de % de stock de seguridad, segun la banda de variabilidad del Modulo 5. El % se aplica sobre la cobertura base (DDI minimo = 1.5x lead time), NO sobre el capital ni sobre el inventario final. Formula: Inventario objetivo = venta diaria x cobertura base x (1 + % seguridad).</t>
   </si>
   <si>
     <t xml:space="preserve">La Parte C decide donde pararse DENTRO de este rango, no fuera de el.</t>
@@ -588,6 +594,15 @@
   </si>
   <si>
     <t xml:space="preserve">1.5 x lead_time_dias del subgrupo -- piso para sobrevivir un ciclo y medio de reposicion sin quiebre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPORTANTE: sobre que se aplica el % de stock de seguridad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventario objetivo = venta diaria x cobertura base x (1 + % seguridad). Cobertura base = DDI minimo (1.5x lead time).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El % NO se aplica sobre el capital ni sobre el inventario final -- se aplica sobre los dias de cobertura base.</t>
   </si>
 </sst>
 </file>
@@ -741,92 +756,88 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1085,104 +1096,104 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1205,128 +1216,136 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+    <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="13" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="13" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="B17" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C17" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="9" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="B18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="9" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="B19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C19" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="9" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="B20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="9" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+      <c r="B21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C21" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="9" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
         <v>46</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1351,154 +1370,154 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>47</v>
+      <c r="A1" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>51</v>
       </c>
+      <c r="C3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>54</v>
       </c>
+      <c r="B4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
+      <c r="B5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>60</v>
       </c>
+      <c r="B6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="A7" s="8" t="s">
         <v>63</v>
       </c>
+      <c r="B7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="A8" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="B8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="6" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>69</v>
       </c>
+      <c r="B9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="A10" s="8" t="s">
         <v>72</v>
       </c>
+      <c r="B10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>76</v>
       </c>
+      <c r="C11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="A12" s="8" t="s">
         <v>79</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1520,647 +1539,647 @@
   <dimension ref="A1:V13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>80</v>
+      <c r="A1" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
+      <c r="A2" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="H5" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="I5" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="J5" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="K5" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="L5" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="M5" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="N5" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="O5" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="P5" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="Q5" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="R5" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="U5" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="V5" s="13" t="s">
-        <v>58</v>
+      <c r="S5" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="T5" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="U5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="15" t="n">
+      <c r="B6" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="14" t="n">
         <v>9800</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="14" t="n">
         <v>8300</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="14" t="n">
         <v>4400</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="14" t="n">
         <v>1200</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="14" t="n">
         <v>750</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="14" t="n">
         <v>800</v>
       </c>
-      <c r="K6" s="15" t="n">
+      <c r="K6" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="L6" s="15" t="n">
+      <c r="L6" s="14" t="n">
         <v>1700</v>
       </c>
-      <c r="M6" s="15" t="n">
+      <c r="M6" s="14" t="n">
         <v>3400</v>
       </c>
-      <c r="N6" s="15" t="n">
+      <c r="N6" s="14" t="n">
         <v>7300</v>
       </c>
-      <c r="O6" s="15" t="n">
+      <c r="O6" s="14" t="n">
         <v>10800</v>
       </c>
-      <c r="P6" s="16" t="n">
+      <c r="P6" s="15" t="n">
         <v>9.5</v>
       </c>
-      <c r="Q6" s="16" t="n">
+      <c r="Q6" s="15" t="n">
         <v>5.2</v>
       </c>
-      <c r="R6" s="15" t="n">
+      <c r="R6" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="S6" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="T6" s="15" t="n">
-        <v>10572</v>
-      </c>
-      <c r="U6" s="15" t="s">
+      <c r="S6" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="T6" s="14" t="n">
+        <v>6484</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="V6" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="V6" s="17" t="s">
+      <c r="D7" s="14" t="n">
+        <v>8800</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>11800</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>750</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>5900</v>
+      </c>
+      <c r="O7" s="14" t="n">
+        <v>10300</v>
+      </c>
+      <c r="P7" s="15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Q7" s="15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R7" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="S7" s="14" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="T7" s="14" t="n">
+        <v>4234</v>
+      </c>
+      <c r="U7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>8800</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>11800</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>2900</v>
-      </c>
-      <c r="G7" s="15" t="n">
+      <c r="V7" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>4050</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>4450</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>4700</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>5200</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>5900</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>6150</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>5650</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>4900</v>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>4450</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>4300</v>
+      </c>
+      <c r="O8" s="14" t="n">
+        <v>4450</v>
+      </c>
+      <c r="P8" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="R8" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="S8" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="T8" s="14" t="n">
+        <v>6080</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="V8" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>2080</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>2030</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>1980</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>2010</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>2030</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>2050</v>
+      </c>
+      <c r="O9" s="14" t="n">
+        <v>2080</v>
+      </c>
+      <c r="P9" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="R9" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="T9" s="14" t="n">
+        <v>2196</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="V9" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>5450</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>6450</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>7450</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>8450</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>8700</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>7950</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>5700</v>
+      </c>
+      <c r="N10" s="14" t="n">
+        <v>5450</v>
+      </c>
+      <c r="O10" s="14" t="n">
+        <v>5700</v>
+      </c>
+      <c r="P10" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q10" s="15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="T10" s="14" t="n">
+        <v>2801</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="V10" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>590</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>470</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>890</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>540</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>990</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>440</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1240</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>490</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>690</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>1040</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>470</v>
+      </c>
+      <c r="O11" s="14" t="n">
+        <v>790</v>
+      </c>
+      <c r="P11" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="R11" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="S11" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="T11" s="14" t="n">
+        <v>2178</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="V11" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>270</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>320</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="L12" s="14" t="n">
         <v>750</v>
       </c>
-      <c r="H7" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>350</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="L7" s="15" t="n">
+      <c r="M12" s="14" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>900</v>
+      </c>
+      <c r="O12" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P12" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="R12" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="S12" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="T12" s="14" t="n">
+        <v>2360</v>
+      </c>
+      <c r="U12" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="V12" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="M7" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N7" s="15" t="n">
-        <v>5900</v>
-      </c>
-      <c r="O7" s="15" t="n">
-        <v>10300</v>
-      </c>
-      <c r="P7" s="16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Q7" s="16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="S7" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="T7" s="15" t="n">
-        <v>4981</v>
-      </c>
-      <c r="U7" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="V7" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>4200</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>4050</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>4450</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>4700</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>5200</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>5900</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>6150</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>5650</v>
-      </c>
-      <c r="L8" s="15" t="n">
-        <v>4900</v>
-      </c>
-      <c r="M8" s="15" t="n">
-        <v>4450</v>
-      </c>
-      <c r="N8" s="15" t="n">
-        <v>4300</v>
-      </c>
-      <c r="O8" s="15" t="n">
-        <v>4450</v>
-      </c>
-      <c r="P8" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q8" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="R8" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="S8" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="T8" s="15" t="n">
-        <v>8800</v>
-      </c>
-      <c r="U8" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="V8" s="17" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>1960</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>2030</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>2010</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>2050</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>2080</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>2030</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>1980</v>
-      </c>
-      <c r="L9" s="15" t="n">
-        <v>2010</v>
-      </c>
-      <c r="M9" s="15" t="n">
-        <v>2030</v>
-      </c>
-      <c r="N9" s="15" t="n">
-        <v>2050</v>
-      </c>
-      <c r="O9" s="15" t="n">
-        <v>2080</v>
-      </c>
-      <c r="P9" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q9" s="16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="R9" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="S9" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="T9" s="15" t="n">
-        <v>3993</v>
-      </c>
-      <c r="U9" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="V9" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>5450</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>6450</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>7450</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>8450</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>8700</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>7950</v>
-      </c>
-      <c r="L10" s="15" t="n">
-        <v>6450</v>
-      </c>
-      <c r="M10" s="15" t="n">
-        <v>5700</v>
-      </c>
-      <c r="N10" s="15" t="n">
-        <v>5450</v>
-      </c>
-      <c r="O10" s="15" t="n">
-        <v>5700</v>
-      </c>
-      <c r="P10" s="16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q10" s="16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R10" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="S10" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="T10" s="15" t="n">
-        <v>4310</v>
-      </c>
-      <c r="U10" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="V10" s="17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>590</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>470</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>890</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>540</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>990</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>440</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>490</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <v>690</v>
-      </c>
-      <c r="M11" s="15" t="n">
-        <v>1040</v>
-      </c>
-      <c r="N11" s="15" t="n">
-        <v>470</v>
-      </c>
-      <c r="O11" s="15" t="n">
-        <v>790</v>
-      </c>
-      <c r="P11" s="16" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q11" s="16" t="n">
-        <v>24</v>
-      </c>
-      <c r="R11" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="S11" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="T11" s="15" t="n">
-        <v>2604</v>
-      </c>
-      <c r="U11" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="V11" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>270</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>350</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>320</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>350</v>
-      </c>
-      <c r="L12" s="15" t="n">
+      <c r="E13" s="14" t="n">
         <v>750</v>
       </c>
-      <c r="M12" s="15" t="n">
-        <v>1600</v>
-      </c>
-      <c r="N12" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="O12" s="15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P12" s="16" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q12" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="R12" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="S12" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="T12" s="15" t="n">
-        <v>2950</v>
-      </c>
-      <c r="U12" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="V12" s="17" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>750</v>
-      </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="14" t="n">
         <v>650</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="14" t="n">
         <v>700</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="14" t="n">
         <v>650</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="14" t="n">
         <v>700</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K13" s="14" t="n">
         <v>800</v>
       </c>
-      <c r="L13" s="15" t="n">
+      <c r="L13" s="14" t="n">
         <v>1500</v>
       </c>
-      <c r="M13" s="15" t="n">
+      <c r="M13" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="N13" s="15" t="n">
+      <c r="N13" s="14" t="n">
         <v>1750</v>
       </c>
-      <c r="O13" s="15" t="n">
+      <c r="O13" s="14" t="n">
         <v>4500</v>
       </c>
-      <c r="P13" s="16" t="n">
+      <c r="P13" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="Q13" s="16" t="n">
+      <c r="Q13" s="15" t="n">
         <v>8.5</v>
       </c>
-      <c r="R13" s="15" t="n">
+      <c r="R13" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="S13" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="T13" s="15" t="n">
-        <v>4093</v>
-      </c>
-      <c r="U13" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="V13" s="17" t="s">
-        <v>127</v>
+      <c r="S13" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="T13" s="14" t="n">
+        <v>2820</v>
+      </c>
+      <c r="U13" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="V13" s="16" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2185,148 +2204,148 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>128</v>
+      <c r="A1" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="19"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2356,143 +2375,143 @@
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>132</v>
+      <c r="A1" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
+      <c r="A2" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="13" t="s">
+      <c r="A4" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>139</v>
       </c>
+      <c r="F4" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="A5" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="A6" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
+      <c r="A7" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="A8" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="A9" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
+      <c r="A10" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
+      <c r="A11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="A12" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2516,402 +2535,402 @@
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>140</v>
+      <c r="A1" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="A2" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>142</v>
+      <c r="A4" s="2" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="A5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>149</v>
       </c>
+      <c r="H5" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="A6" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
+      <c r="A7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
+      <c r="A8" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="A9" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="A10" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="A11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
+      <c r="A12" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
+      <c r="A13" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="17"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="17"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="17"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="17"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="H24" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="18"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="I24" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="C17" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C18" s="18"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="C35" s="17"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="18"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+      <c r="C36" s="17"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="18"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="C37" s="17"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C35" s="18"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C36" s="18"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C37" s="18"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C38" s="18"/>
+      <c r="C38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C39" s="18"/>
+      <c r="A39" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2932,160 +2951,191 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>156</v>
+      <c r="A1" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>84</v>
+      <c r="A3" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="F4" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>103</v>
+      <c r="A4" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="F4" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="B5" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="20" t="s">
-        <v>119</v>
+      <c r="D5" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="C6" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="D6" s="8" t="s">
         <v>169</v>
       </c>
+      <c r="F6" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="C7" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>177</v>
       </c>
+      <c r="C8" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>181</v>
       </c>
+      <c r="C9" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>185</v>
       </c>
+      <c r="C10" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>70</v>
+      <c r="A13" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
+      <c r="A14" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
